--- a/public/exports-from-60-with-coowners/29189765.xlsx
+++ b/public/exports-from-60-with-coowners/29189765.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189765.xlsx
+++ b/public/exports-from-60-with-coowners/29189765.xlsx
@@ -1466,7 +1466,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 389</t>
+          <t xml:space="preserve">Fælledvej 3B</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1476,30 +1476,30 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1493949</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J20">
-        <v>90</v>
+        <v>1170</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025297</t>
+          <t xml:space="preserve">200034119</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-10</t>
+          <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fælledvej 3B</t>
+          <t xml:space="preserve">Tingparken 60</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1551,30 +1551,30 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">5142648</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J21">
-        <v>1170</v>
+        <v>767</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034119</t>
+          <t xml:space="preserve">200058964</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Grontmij A/S (Kolding)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-15</t>
+          <t xml:space="preserve">2022-04-18</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingparken 60</t>
+          <t xml:space="preserve">Tingparken 62</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1631,11 +1631,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J22">
-        <v>767</v>
+        <v>592</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1691,17 +1691,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingparken 62</t>
+          <t xml:space="preserve">Egebjerg Landevej 82</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142648</t>
+          <t xml:space="preserve">735123, 5144023</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="J23">
-        <v>592</v>
+        <v>705</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058964</t>
+          <t xml:space="preserve">200059041</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grontmij A/S (Kolding)</t>
+          <t xml:space="preserve">JA-Byggerådgivning</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-18</t>
+          <t xml:space="preserve">2022-04-21</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1766,50 +1766,50 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egebjerg Landevej 82</t>
+          <t xml:space="preserve">Skovvej 12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7260</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">735123, 5144023</t>
+          <t xml:space="preserve">735111, 4358383</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J24">
-        <v>705</v>
+        <v>424</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059041</t>
+          <t xml:space="preserve">311376125</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">JA-Byggerådgivning</t>
+          <t xml:space="preserve">PAARUP arkitekter</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-21</t>
+          <t xml:space="preserve">2029-05-10</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1841,40 +1841,40 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 12</t>
+          <t xml:space="preserve">Søndervold 350</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">735111, 4358383</t>
+          <t xml:space="preserve">100091449</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J25">
-        <v>424</v>
+        <v>1949</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376125</t>
+          <t xml:space="preserve">311380467</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAARUP arkitekter</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-10</t>
+          <t xml:space="preserve">2029-06-03</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billund Kommune</t>
+          <t xml:space="preserve">BILLUND BOLIGFORENING</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1916,17 +1916,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndervold 350</t>
+          <t xml:space="preserve">Vejlevej 1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">100091449</t>
+          <t xml:space="preserve">100391605, 100391606, 100391607</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="J26">
-        <v>1949</v>
+        <v>6525</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311380467</t>
+          <t xml:space="preserve">311543018</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Højbjerg Energimærkning</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-03</t>
+          <t xml:space="preserve">2031-08-24</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">BILLUND BOLIGFORENING</t>
+          <t xml:space="preserve">Billund Kommune</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlevej 1</t>
+          <t xml:space="preserve">Tårnvej 30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">100391605, 100391606, 100391607</t>
+          <t xml:space="preserve">5138663</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2010,21 +2010,21 @@
         </is>
       </c>
       <c r="J27">
-        <v>6525</v>
+        <v>360</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543018</t>
+          <t xml:space="preserve">311612418</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højbjerg Energimærkning</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-24</t>
+          <t xml:space="preserve">2032-07-01</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tårnvej 30</t>
+          <t xml:space="preserve">Billundvej 7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138663</t>
+          <t xml:space="preserve">5144094</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2085,11 +2085,11 @@
         </is>
       </c>
       <c r="J28">
-        <v>360</v>
+        <v>156</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612418</t>
+          <t xml:space="preserve">311622997</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-01</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2156,15 +2156,15 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J29">
-        <v>156</v>
+        <v>523</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622997</t>
+          <t xml:space="preserve">311622731</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billundvej 7</t>
+          <t xml:space="preserve">Torvegade 9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5144094</t>
+          <t xml:space="preserve">10125671</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2235,11 +2235,11 @@
         </is>
       </c>
       <c r="J30">
-        <v>523</v>
+        <v>374</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622731</t>
+          <t xml:space="preserve">311622674</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2291,30 +2291,30 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 9</t>
+          <t xml:space="preserve">Havremarken 10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">10125671</t>
+          <t xml:space="preserve">7142775</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J31">
-        <v>374</v>
+        <v>237</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622674</t>
+          <t xml:space="preserve">311622356</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havremarken 10</t>
+          <t xml:space="preserve">Kærvej 503</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7142775</t>
+          <t xml:space="preserve">5136097</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2385,11 +2385,11 @@
         </is>
       </c>
       <c r="J32">
-        <v>237</v>
+        <v>13031</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622356</t>
+          <t xml:space="preserve">311622983</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 503</t>
+          <t xml:space="preserve">Kærvej 501</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2456,15 +2456,15 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J33">
-        <v>13031</v>
+        <v>3592</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622983</t>
+          <t xml:space="preserve">311623383</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2531,11 +2531,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J34">
-        <v>3592</v>
+        <v>782</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2606,11 +2606,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J35">
-        <v>782</v>
+        <v>1200</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2666,30 +2666,30 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 501</t>
+          <t xml:space="preserve">Fælledvej 3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136097</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J36">
-        <v>1200</v>
+        <v>11890</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623383</t>
+          <t xml:space="preserve">311624675</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fælledvej 3</t>
+          <t xml:space="preserve">Jorden Rundt 1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">5142428</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2760,11 +2760,11 @@
         </is>
       </c>
       <c r="J37">
-        <v>11890</v>
+        <v>6962</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624675</t>
+          <t xml:space="preserve">311624665</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jorden Rundt 1</t>
+          <t xml:space="preserve">Tinghusgade 7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,20 +2826,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142428</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J38">
-        <v>6962</v>
+        <v>306</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624665</t>
+          <t xml:space="preserve">311632288</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-01</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 7</t>
+          <t xml:space="preserve">Tinghusgade 7B</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2906,15 +2906,15 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J39">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632288</t>
+          <t xml:space="preserve">311632292</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 7B</t>
+          <t xml:space="preserve">Tinghusgade 9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2981,15 +2981,15 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>79</v>
+        <v>3488</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632292</t>
+          <t xml:space="preserve">311632318</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3056,15 +3056,15 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J41">
-        <v>3488</v>
+        <v>709</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632318</t>
+          <t xml:space="preserve">311632299</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3131,15 +3131,15 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J42">
-        <v>709</v>
+        <v>3414</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632299</t>
+          <t xml:space="preserve">311632278</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3206,15 +3206,15 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J43">
-        <v>3414</v>
+        <v>345</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632278</t>
+          <t xml:space="preserve">311632285</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3281,15 +3281,15 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J44">
-        <v>345</v>
+        <v>1536</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632285</t>
+          <t xml:space="preserve">311632306</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 9</t>
+          <t xml:space="preserve">Tårnvej 135</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,20 +3351,20 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">5138708</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J45">
-        <v>1536</v>
+        <v>1592</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632306</t>
+          <t xml:space="preserve">311633484</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tårnvej 135</t>
+          <t xml:space="preserve">Tårnvej 135A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3431,11 +3431,11 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J46">
-        <v>1592</v>
+        <v>929</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tårnvej 135A</t>
+          <t xml:space="preserve">Tårnvej 135B</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3506,11 +3506,11 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J47">
-        <v>929</v>
+        <v>681</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3566,30 +3566,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tårnvej 135B</t>
+          <t xml:space="preserve">Bakkevej 9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138708</t>
+          <t xml:space="preserve">5144271</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>681</v>
+        <v>8226</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633484</t>
+          <t xml:space="preserve">311638729</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-05</t>
+          <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3656,20 +3656,20 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J49">
-        <v>8226</v>
+        <v>211</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311638729</t>
+          <t xml:space="preserve">311638702</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3716,40 +3716,40 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 9</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5144271</t>
+          <t xml:space="preserve">321347, 321348, 321350</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J50">
-        <v>211</v>
+        <v>6736</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311638702</t>
+          <t xml:space="preserve">311639923</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Factum2 A/S</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-27</t>
+          <t xml:space="preserve">2032-11-02</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Sydtoften 167</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">321347, 321348, 321350</t>
+          <t xml:space="preserve">5143076</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,21 +3810,21 @@
         </is>
       </c>
       <c r="J51">
-        <v>6736</v>
+        <v>328</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639923</t>
+          <t xml:space="preserve">311646998</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factum2 A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-02</t>
+          <t xml:space="preserve">2032-12-05</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 167</t>
+          <t xml:space="preserve">Sydtoften 4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5143076</t>
+          <t xml:space="preserve">5142923</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3885,11 +3885,11 @@
         </is>
       </c>
       <c r="J52">
-        <v>328</v>
+        <v>511</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646998</t>
+          <t xml:space="preserve">311647593</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-05</t>
+          <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 4</t>
+          <t xml:space="preserve">Vesterbrogade 5C</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142923</t>
+          <t xml:space="preserve">7000541</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="J53">
-        <v>511</v>
+        <v>1547</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647593</t>
+          <t xml:space="preserve">311649283</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-07</t>
+          <t xml:space="preserve">2032-12-14</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbrogade 5C</t>
+          <t xml:space="preserve">Borgergade 38</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000541</t>
+          <t xml:space="preserve">5138751</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="J54">
-        <v>1547</v>
+        <v>371</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649283</t>
+          <t xml:space="preserve">311650121</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-14</t>
+          <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 38</t>
+          <t xml:space="preserve">Industrivej 14E</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138751</t>
+          <t xml:space="preserve">7809482</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4110,11 +4110,11 @@
         </is>
       </c>
       <c r="J55">
-        <v>371</v>
+        <v>224</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650121</t>
+          <t xml:space="preserve">311650119</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 14E</t>
+          <t xml:space="preserve">Trehøjevej 18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7809482</t>
+          <t xml:space="preserve">8289340</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4185,11 +4185,11 @@
         </is>
       </c>
       <c r="J56">
-        <v>224</v>
+        <v>550</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650119</t>
+          <t xml:space="preserve">311650123</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trehøjevej 18</t>
+          <t xml:space="preserve">Kærvej 124</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8289340</t>
+          <t xml:space="preserve">5136092</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4260,11 +4260,11 @@
         </is>
       </c>
       <c r="J57">
-        <v>550</v>
+        <v>486</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650123</t>
+          <t xml:space="preserve">311650984</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-19</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 124</t>
+          <t xml:space="preserve">Granvej 5A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136092</t>
+          <t xml:space="preserve">100066951</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="J58">
-        <v>486</v>
+        <v>361</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650984</t>
+          <t xml:space="preserve">311652147</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-01-03</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granvej 5A</t>
+          <t xml:space="preserve">Skolevej 18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,20 +4401,20 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">100066951</t>
+          <t xml:space="preserve">7765432</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J59">
-        <v>361</v>
+        <v>181</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652147</t>
+          <t xml:space="preserve">311652157</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4466,30 +4466,30 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 18</t>
+          <t xml:space="preserve">Rolighedsvej 8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7765432</t>
+          <t xml:space="preserve">5139666</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>181</v>
+        <v>585</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652157</t>
+          <t xml:space="preserve">311652537</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-03</t>
+          <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 8</t>
+          <t xml:space="preserve">Tuen 2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5139666</t>
+          <t xml:space="preserve">7870009</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>585</v>
+        <v>715</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652537</t>
+          <t xml:space="preserve">311652985</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-05</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuen 2</t>
+          <t xml:space="preserve">Vestergade 122</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870009</t>
+          <t xml:space="preserve">5140427</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="J62">
-        <v>715</v>
+        <v>482</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652985</t>
+          <t xml:space="preserve">311653312</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2033-01-10</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 122</t>
+          <t xml:space="preserve">Drivvejen 34</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6623</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140427</t>
+          <t xml:space="preserve">5146083</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>482</v>
+        <v>146</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653312</t>
+          <t xml:space="preserve">311653474</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-10</t>
+          <t xml:space="preserve">2033-01-11</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drivvejen 34</t>
+          <t xml:space="preserve">Østergade 25A</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6623</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146083</t>
+          <t xml:space="preserve">5140770</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>146</v>
+        <v>654</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653474</t>
+          <t xml:space="preserve">311653561</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 25A</t>
+          <t xml:space="preserve">Østergade 27A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4856,11 +4856,11 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J65">
-        <v>654</v>
+        <v>199</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 27A</t>
+          <t xml:space="preserve">Søndre Boulevard 13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,30 +4926,30 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140770</t>
+          <t xml:space="preserve">7796007</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J66">
-        <v>199</v>
+        <v>268</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653561</t>
+          <t xml:space="preserve">311653615</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-11</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,40 +4991,40 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Boulevard 13</t>
+          <t xml:space="preserve">Kirke Alle 7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7260</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7796007</t>
+          <t xml:space="preserve">8362229</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J67">
-        <v>268</v>
+        <v>5803</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653615</t>
+          <t xml:space="preserve">311655183</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,30 +5066,30 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Alle 7</t>
+          <t xml:space="preserve">Engdraget 8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8362229</t>
+          <t xml:space="preserve">7565490</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J68">
-        <v>5803</v>
+        <v>2036</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655183</t>
+          <t xml:space="preserve">311656709</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-20</t>
+          <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,30 +5141,30 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 8</t>
+          <t xml:space="preserve">Stadionvej 1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">6623</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7565490</t>
+          <t xml:space="preserve">5145779</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J69">
-        <v>2036</v>
+        <v>145</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656709</t>
+          <t xml:space="preserve">311659209</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 1</t>
+          <t xml:space="preserve">Stadionvej 9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5231,15 +5231,15 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J70">
-        <v>145</v>
+        <v>1546</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659209</t>
+          <t xml:space="preserve">311659176</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5306,11 +5306,11 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J71">
-        <v>1546</v>
+        <v>4252</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5381,11 +5381,11 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J72">
-        <v>4252</v>
+        <v>85</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9</t>
+          <t xml:space="preserve">Drivvejen 3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5145779</t>
+          <t xml:space="preserve">5146067</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="J73">
-        <v>85</v>
+        <v>566</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659176</t>
+          <t xml:space="preserve">311659784</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-02-13</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,30 +5516,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drivvejen 3</t>
+          <t xml:space="preserve">Vesterhedevej 9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6623</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146067</t>
+          <t xml:space="preserve">5142513</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>566</v>
+        <v>91</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659784</t>
+          <t xml:space="preserve">311664917</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-13</t>
+          <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterhedevej 9</t>
+          <t xml:space="preserve">Nymarksvej 10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142513</t>
+          <t xml:space="preserve">5140009</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,11 +5610,11 @@
         </is>
       </c>
       <c r="J75">
-        <v>91</v>
+        <v>1474</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664917</t>
+          <t xml:space="preserve">311665113</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-08</t>
+          <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymarksvej 10</t>
+          <t xml:space="preserve">Banegårdsvej 24A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,20 +5676,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140009</t>
+          <t xml:space="preserve">5138720</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J76">
-        <v>1474</v>
+        <v>529</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665113</t>
+          <t xml:space="preserve">311667938</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-09</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdsvej 24A</t>
+          <t xml:space="preserve">Banegårdsvej 26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5756,11 +5756,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J77">
-        <v>529</v>
+        <v>1186</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdsvej 26</t>
+          <t xml:space="preserve">Fælledvej 3A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138720</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J78">
-        <v>1186</v>
+        <v>449</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667938</t>
+          <t xml:space="preserve">311667996</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fælledvej 3A</t>
+          <t xml:space="preserve">Vestermarksvej 2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5906,15 +5906,15 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J79">
-        <v>449</v>
+        <v>1036</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667996</t>
+          <t xml:space="preserve">311668340</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,30 +5966,30 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarksvej 2</t>
+          <t xml:space="preserve">Løvlundvej 4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">9761698</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J80">
-        <v>1036</v>
+        <v>217</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668340</t>
+          <t xml:space="preserve">311670678</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løvlundvej 4</t>
+          <t xml:space="preserve">Lindevej 1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,20 +6051,20 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9761698</t>
+          <t xml:space="preserve">321345</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J81">
-        <v>217</v>
+        <v>679</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670678</t>
+          <t xml:space="preserve">311671681</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 1</t>
+          <t xml:space="preserve">Lindevej 13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,20 +6126,20 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">321345</t>
+          <t xml:space="preserve">321346</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J82">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671681</t>
+          <t xml:space="preserve">311671684</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 13</t>
+          <t xml:space="preserve">Lindevej 23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J83">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 23</t>
+          <t xml:space="preserve">Lindevej 3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J84">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 3</t>
+          <t xml:space="preserve">Sydtoften 8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">321346</t>
+          <t xml:space="preserve">7951035</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="J85">
-        <v>690</v>
+        <v>529</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671684</t>
+          <t xml:space="preserve">311671706</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 8</t>
+          <t xml:space="preserve">Engvej 12A</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7951035</t>
+          <t xml:space="preserve">5139665</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6435,11 +6435,11 @@
         </is>
       </c>
       <c r="J86">
-        <v>529</v>
+        <v>408</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671706</t>
+          <t xml:space="preserve">311673253</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-04</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 12A</t>
+          <t xml:space="preserve">Morsbølvej 100</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,20 +6501,20 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5139665</t>
+          <t xml:space="preserve">7653714</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J87">
-        <v>408</v>
+        <v>233</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673253</t>
+          <t xml:space="preserve">311674959</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-04-20</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morsbølvej 100</t>
+          <t xml:space="preserve">Morsbølvej 101</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6581,15 +6581,15 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J88">
-        <v>233</v>
+        <v>638</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674959</t>
+          <t xml:space="preserve">311675169</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-20</t>
+          <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,30 +6641,30 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morsbølvej 101</t>
+          <t xml:space="preserve">Skolevej 12A</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">7653714</t>
+          <t xml:space="preserve">9723509</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J89">
-        <v>638</v>
+        <v>751</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675169</t>
+          <t xml:space="preserve">311676118</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-21</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 12A</t>
+          <t xml:space="preserve">Skolevej 12F</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6731,11 +6731,11 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J90">
-        <v>751</v>
+        <v>87</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 12F</t>
+          <t xml:space="preserve">Hans Jensensvej 6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,20 +6801,20 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9723509</t>
+          <t xml:space="preserve">5136614</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J91">
-        <v>87</v>
+        <v>3395</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676118</t>
+          <t xml:space="preserve">311677651</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-25</t>
+          <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,40 +6866,40 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Jensensvej 6</t>
+          <t xml:space="preserve">Langelandsvej 70</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136614</t>
+          <t xml:space="preserve">5140426</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J92">
-        <v>3395</v>
+        <v>2001</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677651</t>
+          <t xml:space="preserve">311679640</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-01</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langelandsvej 70</t>
+          <t xml:space="preserve">Tingvejen 383A</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,20 +6951,20 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140426</t>
+          <t xml:space="preserve">100012410</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J93">
-        <v>2001</v>
+        <v>208</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679640</t>
+          <t xml:space="preserve">311679345</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 383A</t>
+          <t xml:space="preserve">Tingvejen 383D</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J94">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 383D</t>
+          <t xml:space="preserve">Jørgen Glavinds Vej 2F</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">100012410</t>
+          <t xml:space="preserve">5142582</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7110,21 +7110,21 @@
         </is>
       </c>
       <c r="J95">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679345</t>
+          <t xml:space="preserve">311680381</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group af 2017 ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 385A</t>
+          <t xml:space="preserve">Tinghusgade 15A</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,30 +7176,30 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1493949</t>
+          <t xml:space="preserve">5142582</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J96">
-        <v>1140</v>
+        <v>2235</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679342</t>
+          <t xml:space="preserve">311680381</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group af 2017 ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jørgen Glavinds Vej 2F</t>
+          <t xml:space="preserve">Tinghusgade 15C</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J97">
-        <v>207</v>
+        <v>1811</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 15A</t>
+          <t xml:space="preserve">Tinghusgade 15F</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7331,11 +7331,11 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J98">
-        <v>2235</v>
+        <v>3334</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 15C</t>
+          <t xml:space="preserve">Fynsgade 33</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,30 +7401,30 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142582</t>
+          <t xml:space="preserve">315128</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J99">
-        <v>1811</v>
+        <v>184</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680381</t>
+          <t xml:space="preserve">311684237</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2033-05-31</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 15F</t>
+          <t xml:space="preserve">Fynsgade 39</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142582</t>
+          <t xml:space="preserve">315128, 315129, 315130</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="J100">
-        <v>3334</v>
+        <v>3456</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680381</t>
+          <t xml:space="preserve">311684239</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2033-05-31</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fynsgade 33</t>
+          <t xml:space="preserve">Sydtoften 100A</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,20 +7551,20 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">315128</t>
+          <t xml:space="preserve">315575, 315578</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J101">
-        <v>184</v>
+        <v>653</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684237</t>
+          <t xml:space="preserve">311684378</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fynsgade 39</t>
+          <t xml:space="preserve">Sydtoften 102</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">315128, 315129, 315130</t>
+          <t xml:space="preserve">315575, 315576</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7635,11 +7635,11 @@
         </is>
       </c>
       <c r="J102">
-        <v>3456</v>
+        <v>2655</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684239</t>
+          <t xml:space="preserve">311684376</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 100A</t>
+          <t xml:space="preserve">Buen 6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,30 +7701,30 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">315575, 315578</t>
+          <t xml:space="preserve">9084190</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J103">
-        <v>653</v>
+        <v>607</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684378</t>
+          <t xml:space="preserve">311686103</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group af 2017 ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-31</t>
+          <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 102</t>
+          <t xml:space="preserve">Buen 6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,30 +7776,30 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">315575, 315576</t>
+          <t xml:space="preserve">9084190</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J104">
-        <v>2655</v>
+        <v>1457</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684376</t>
+          <t xml:space="preserve">311686103</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group af 2017 ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-31</t>
+          <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 6</t>
+          <t xml:space="preserve">Degnelodden 3</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6623</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9084190</t>
+          <t xml:space="preserve">315952, 315953, 315954</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>607</v>
+        <v>2824</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686103</t>
+          <t xml:space="preserve">311686146</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,30 +7916,30 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 6</t>
+          <t xml:space="preserve">Drivvejen 1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6623</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9084190</t>
+          <t xml:space="preserve">5146067</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>1457</v>
+        <v>6667</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686103</t>
+          <t xml:space="preserve">311686166</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7991,17 +7991,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnelodden 3</t>
+          <t xml:space="preserve">Kirkevej 8A</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6623</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">315952, 315953, 315954</t>
+          <t xml:space="preserve">315561, 315562, 315563, 315564</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,11 +8010,11 @@
         </is>
       </c>
       <c r="J107">
-        <v>2824</v>
+        <v>1775</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686146</t>
+          <t xml:space="preserve">311686186</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,30 +8066,30 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drivvejen 1</t>
+          <t xml:space="preserve">Kirkevej 8B</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6623</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146067</t>
+          <t xml:space="preserve">315563</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J108">
-        <v>6667</v>
+        <v>264</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686166</t>
+          <t xml:space="preserve">311686187</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 8A</t>
+          <t xml:space="preserve">Rahbæksvej 18</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7260</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">315561, 315562, 315563, 315564</t>
+          <t xml:space="preserve">321325, 321326, 321327</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="J109">
-        <v>1775</v>
+        <v>3813</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686186</t>
+          <t xml:space="preserve">311686196</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,30 +8216,30 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 8B</t>
+          <t xml:space="preserve">Teglgaardsvej 7</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">315563</t>
+          <t xml:space="preserve">735144, 5077351</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J110">
-        <v>264</v>
+        <v>1538</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686187</t>
+          <t xml:space="preserve">311686096</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rahbæksvej 18</t>
+          <t xml:space="preserve">Tinghusgade 12</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">321325, 321326, 321327</t>
+          <t xml:space="preserve">5142495</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J111">
-        <v>3813</v>
+        <v>2526</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686196</t>
+          <t xml:space="preserve">311686205</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgaardsvej 7</t>
+          <t xml:space="preserve">Tinghusgade 16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,20 +8376,20 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">735144, 5077351</t>
+          <t xml:space="preserve">5142495</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J112">
-        <v>1538</v>
+        <v>1991</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686096</t>
+          <t xml:space="preserve">311686199</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billund Kommune</t>
+          <t xml:space="preserve">Hedens Boligselskab</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 12</t>
+          <t xml:space="preserve">Sydtoften 381B</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,30 +8451,30 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142495</t>
+          <t xml:space="preserve">315579, 315580</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>2526</v>
+        <v>1757</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686205</t>
+          <t xml:space="preserve">311711256</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-07</t>
+          <t xml:space="preserve">2033-09-28</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billund Kommune</t>
+          <t xml:space="preserve">Hedens Boligselskab</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 16</t>
+          <t xml:space="preserve">Nygade 29</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142495</t>
+          <t xml:space="preserve">315080, 315082</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,21 +8535,21 @@
         </is>
       </c>
       <c r="J114">
-        <v>1991</v>
+        <v>3573</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686199</t>
+          <t xml:space="preserve">311711550</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-07</t>
+          <t xml:space="preserve">2033-09-29</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedens Boligselskab</t>
+          <t xml:space="preserve">Billund Kommune</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8591,30 +8591,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 381B</t>
+          <t xml:space="preserve">Skolevej 8</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">315579, 315580</t>
+          <t xml:space="preserve">321349</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J115">
-        <v>1757</v>
+        <v>114</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711256</t>
+          <t xml:space="preserve">311714553</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-28</t>
+          <t xml:space="preserve">2033-10-12</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedens Boligselskab</t>
+          <t xml:space="preserve">Billund Kommune</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 29</t>
+          <t xml:space="preserve">Vesterbrogade 1A</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">315080, 315082</t>
+          <t xml:space="preserve">9658844</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,21 +8685,21 @@
         </is>
       </c>
       <c r="J116">
-        <v>3573</v>
+        <v>519</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711550</t>
+          <t xml:space="preserve">311735594</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-29</t>
+          <t xml:space="preserve">2034-01-28</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,40 +8741,40 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 8</t>
+          <t xml:space="preserve">Skovvej 15</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7260</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">321349</t>
+          <t xml:space="preserve">9084136</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J117">
-        <v>114</v>
+        <v>1099</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311714553</t>
+          <t xml:space="preserve">311771547</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">STD Klima og Byggeri</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-12</t>
+          <t xml:space="preserve">2034-07-04</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billund Kommune</t>
+          <t xml:space="preserve">KIRKBI Property A/S</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbrogade 1A</t>
+          <t xml:space="preserve">Byens Plads 3</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9658844</t>
+          <t xml:space="preserve">321351, 321352, 321353</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,21 +8835,21 @@
         </is>
       </c>
       <c r="J118">
-        <v>519</v>
+        <v>1478</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735594</t>
+          <t xml:space="preserve">311846016</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-28</t>
+          <t xml:space="preserve">2035-07-24</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,40 +8891,40 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 15</t>
+          <t xml:space="preserve">Tingvejen 385A</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9084136</t>
+          <t xml:space="preserve">1493949</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>1099</v>
+        <v>1140</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771547</t>
+          <t xml:space="preserve">311928758</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD Klima og Byggeri</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-04</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIRKBI Property A/S</t>
+          <t xml:space="preserve">Billund Kommune</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8966,40 +8966,40 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byens Plads 3</t>
+          <t xml:space="preserve">Tingvejen 389</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">321351, 321352, 321353</t>
+          <t xml:space="preserve">1493949</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J120">
-        <v>1478</v>
+        <v>90</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846016</t>
+          <t xml:space="preserve">311928758</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-24</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189765.xlsx
+++ b/public/exports-from-60-with-coowners/29189765.xlsx
@@ -8914,7 +8914,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928758</t>
+          <t xml:space="preserve">311928752</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928758</t>
+          <t xml:space="preserve">311928752</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
